--- a/Assets/Excel/RoleLevel.xlsx
+++ b/Assets/Excel/RoleLevel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OpenBox\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5757EB57-17EB-4D82-9547-681C8027DB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FC5ACE-3F36-4582-8502-1975C64C27DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6825" yWindow="1410" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Int</t>
   </si>
@@ -47,6 +50,14 @@
   </si>
   <si>
     <t>LvUpExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -402,7 +413,9 @@
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -411,7 +424,9 @@
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -420,7 +435,9 @@
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2"/>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -429,6 +446,9 @@
       <c r="B4" s="1">
         <v>100</v>
       </c>
+      <c r="C4" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -437,6 +457,9 @@
       <c r="B5" s="1">
         <v>150</v>
       </c>
+      <c r="C5" s="1">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -445,6 +468,9 @@
       <c r="B6" s="1">
         <v>200</v>
       </c>
+      <c r="C6" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -453,6 +479,9 @@
       <c r="B7" s="1">
         <v>250</v>
       </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -461,6 +490,9 @@
       <c r="B8" s="1">
         <v>300</v>
       </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
@@ -469,6 +501,9 @@
       <c r="B9" s="1">
         <v>350</v>
       </c>
+      <c r="C9" s="1">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -477,6 +512,9 @@
       <c r="B10" s="1">
         <v>400</v>
       </c>
+      <c r="C10" s="1">
+        <v>26</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
@@ -485,6 +523,9 @@
       <c r="B11" s="1">
         <v>450</v>
       </c>
+      <c r="C11" s="1">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -493,6 +534,9 @@
       <c r="B12" s="1">
         <v>500</v>
       </c>
+      <c r="C12" s="1">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -501,6 +545,9 @@
       <c r="B13" s="1">
         <v>550</v>
       </c>
+      <c r="C13" s="1">
+        <v>29</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -509,6 +556,9 @@
       <c r="B14" s="1">
         <v>600</v>
       </c>
+      <c r="C14" s="1">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -517,6 +567,9 @@
       <c r="B15" s="1">
         <v>650</v>
       </c>
+      <c r="C15" s="1">
+        <v>31</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -525,701 +578,965 @@
       <c r="B16" s="1">
         <v>700</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C16" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>14</v>
       </c>
       <c r="B17" s="1">
         <v>750</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C17" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>15</v>
       </c>
       <c r="B18" s="1">
         <v>800</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>16</v>
       </c>
       <c r="B19" s="1">
         <v>850</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>17</v>
       </c>
       <c r="B20" s="1">
         <v>900</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C20" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>18</v>
       </c>
       <c r="B21" s="1">
         <v>950</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C21" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>19</v>
       </c>
       <c r="B22" s="1">
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20</v>
       </c>
       <c r="B23" s="1">
         <v>1050</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C23" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>21</v>
       </c>
       <c r="B24" s="1">
         <v>1100</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C24" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>22</v>
       </c>
       <c r="B25" s="1">
         <v>1150</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C25" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>23</v>
       </c>
       <c r="B26" s="1">
         <v>1200</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C26" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>24</v>
       </c>
       <c r="B27" s="1">
         <v>1250</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C27" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>25</v>
       </c>
       <c r="B28" s="1">
         <v>1300</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C28" s="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>26</v>
       </c>
       <c r="B29" s="1">
         <v>1350</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C29" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>27</v>
       </c>
       <c r="B30" s="1">
         <v>1400</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C30" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>28</v>
       </c>
       <c r="B31" s="1">
         <v>1450</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C31" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>29</v>
       </c>
       <c r="B32" s="1">
         <v>1500</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C32" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>30</v>
       </c>
       <c r="B33" s="1">
         <v>1550</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C33" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>31</v>
       </c>
       <c r="B34" s="1">
         <v>1600</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C34" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>32</v>
       </c>
       <c r="B35" s="1">
         <v>1650</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C35" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>33</v>
       </c>
       <c r="B36" s="1">
         <v>1700</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C36" s="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>34</v>
       </c>
       <c r="B37" s="1">
         <v>1750</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C37" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>35</v>
       </c>
       <c r="B38" s="1">
         <v>1800</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C38" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>36</v>
       </c>
       <c r="B39" s="1">
         <v>1850</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C39" s="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>37</v>
       </c>
       <c r="B40" s="1">
         <v>1900</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C40" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>38</v>
       </c>
       <c r="B41" s="1">
         <v>1950</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C41" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>39</v>
       </c>
       <c r="B42" s="1">
         <v>2000</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C42" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>40</v>
       </c>
       <c r="B43" s="1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C43" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>41</v>
       </c>
       <c r="B44" s="1">
         <v>2100</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C44" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>42</v>
       </c>
       <c r="B45" s="1">
         <v>2150</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C45" s="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>43</v>
       </c>
       <c r="B46" s="1">
         <v>2200</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C46" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>44</v>
       </c>
       <c r="B47" s="1">
         <v>2250</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C47" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>45</v>
       </c>
       <c r="B48" s="1">
         <v>2300</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C48" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>46</v>
       </c>
       <c r="B49" s="1">
         <v>2350</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C49" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>47</v>
       </c>
       <c r="B50" s="1">
         <v>2400</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C50" s="1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>48</v>
       </c>
       <c r="B51" s="1">
         <v>2450</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C51" s="1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>49</v>
       </c>
       <c r="B52" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C52" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>50</v>
       </c>
       <c r="B53" s="1">
         <v>2550</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C53" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>51</v>
       </c>
       <c r="B54" s="1">
         <v>2600</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C54" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>52</v>
       </c>
       <c r="B55" s="1">
         <v>2650</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C55" s="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>53</v>
       </c>
       <c r="B56" s="1">
         <v>2700</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C56" s="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>54</v>
       </c>
       <c r="B57" s="1">
         <v>2750</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C57" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>55</v>
       </c>
       <c r="B58" s="1">
         <v>2800</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C58" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>56</v>
       </c>
       <c r="B59" s="1">
         <v>2850</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C59" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>57</v>
       </c>
       <c r="B60" s="1">
         <v>2900</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C60" s="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>58</v>
       </c>
       <c r="B61" s="1">
         <v>2950</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C61" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>59</v>
       </c>
       <c r="B62" s="1">
         <v>3000</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C62" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>60</v>
       </c>
       <c r="B63" s="1">
         <v>3050</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C63" s="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>61</v>
       </c>
       <c r="B64" s="1">
         <v>3100</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C64" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>62</v>
       </c>
       <c r="B65" s="1">
         <v>3150</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C65" s="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>63</v>
       </c>
       <c r="B66" s="1">
         <v>3200</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C66" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>64</v>
       </c>
       <c r="B67" s="1">
         <v>3250</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C67" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>65</v>
       </c>
       <c r="B68" s="1">
         <v>3300</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C68" s="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>66</v>
       </c>
       <c r="B69" s="1">
         <v>3350</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C69" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>67</v>
       </c>
       <c r="B70" s="1">
         <v>3400</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C70" s="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>68</v>
       </c>
       <c r="B71" s="1">
         <v>3450</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C71" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>69</v>
       </c>
       <c r="B72" s="1">
         <v>3500</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C72" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>70</v>
       </c>
       <c r="B73" s="1">
         <v>3550</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C73" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>71</v>
       </c>
       <c r="B74" s="1">
         <v>3600</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C74" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>72</v>
       </c>
       <c r="B75" s="1">
         <v>3650</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C75" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>73</v>
       </c>
       <c r="B76" s="1">
         <v>3700</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C76" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>74</v>
       </c>
       <c r="B77" s="1">
         <v>3750</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C77" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>75</v>
       </c>
       <c r="B78" s="1">
         <v>3800</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C78" s="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>76</v>
       </c>
       <c r="B79" s="1">
         <v>3850</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C79" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>77</v>
       </c>
       <c r="B80" s="1">
         <v>3900</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C80" s="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>78</v>
       </c>
       <c r="B81" s="1">
         <v>3950</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C81" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>79</v>
       </c>
       <c r="B82" s="1">
         <v>4000</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C82" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>80</v>
       </c>
       <c r="B83" s="1">
         <v>4050</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C83" s="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>81</v>
       </c>
       <c r="B84" s="1">
         <v>4100</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C84" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>82</v>
       </c>
       <c r="B85" s="1">
         <v>4150</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C85" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>83</v>
       </c>
       <c r="B86" s="1">
         <v>4200</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C86" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>84</v>
       </c>
       <c r="B87" s="1">
         <v>4250</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C87" s="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>85</v>
       </c>
       <c r="B88" s="1">
         <v>4300</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C88" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>86</v>
       </c>
       <c r="B89" s="1">
         <v>4350</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C89" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>87</v>
       </c>
       <c r="B90" s="1">
         <v>4400</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C90" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>88</v>
       </c>
       <c r="B91" s="1">
         <v>4450</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C91" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>89</v>
       </c>
       <c r="B92" s="1">
         <v>4500</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C92" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>90</v>
       </c>
       <c r="B93" s="1">
         <v>4550</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C93" s="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>91</v>
       </c>
       <c r="B94" s="1">
         <v>4600</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C94" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>92</v>
       </c>
       <c r="B95" s="1">
         <v>4650</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C95" s="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>93</v>
       </c>
       <c r="B96" s="1">
         <v>4700</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C96" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>94</v>
       </c>
       <c r="B97" s="1">
         <v>4750</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C97" s="1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>95</v>
       </c>
       <c r="B98" s="1">
         <v>4800</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C98" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>96</v>
       </c>
       <c r="B99" s="1">
         <v>4850</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C99" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>97</v>
       </c>
       <c r="B100" s="1">
         <v>4900</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C100" s="1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>98</v>
       </c>
       <c r="B101" s="1">
         <v>4950</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C101" s="1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>99</v>
       </c>
       <c r="B102" s="1">
         <v>5000</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C102" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>100</v>
       </c>
       <c r="B103" s="1">
         <v>5050</v>
+      </c>
+      <c r="C103" s="1">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
